--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test cases'!$A$1:$M$31</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,14 +33,14 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,14 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00203764"/>
-        <bgColor rgb="00203764"/>
+        <fgColor rgb="000F4C81"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,35 +63,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B7C4D1"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B7C4D1"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B7C4D1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B7C4D1"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,24 +452,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -533,12 +523,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Дата рецензування</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Статус кейсу</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>GitHub Issue</t>
         </is>
       </c>
     </row>
@@ -548,33 +543,37 @@
           <t>TC-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>F-10, GUI-10</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Успішний вхід студента за валідними логіном та паролем з переходом до кабінету</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Стенд відкритий; акаунт student активний; користувач не в системі</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Успішний вхід студента з валідними обліковими даними та вихід із системи</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Стенд скинуто (S1). Акаунт student / sandbox24 активний. Chrome 130, нова сесія інкогніто.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити https://sandbox.moodledemo.net/login/index.php
-2. Ввести логін 'student'
-3. Ввести пароль 'sandbox24'
-4. Натиснути кнопку 'Увійти'
-5. У меню користувача натиснути 'Вихід'</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Редірект на /my/; відображається блок 'Мої курси' та профіль 'Student User'. Після кроку 5 сеанс закрито.</t>
+2. У поле «Ім'я входу» ввести student
+3. У поле «Пароль» ввести sandbox24
+4. Натиснути кнопку «Увійти»
+5. У меню користувача натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Сторінка «Вхід до системи» з полями «Ім'я входу», «Пароль», посиланням «Забули пароль?» і кнопками «Увійти», «Увійти як гість».
+2. У полі відображається student.
+3. Символи пароля приховані.
+4. Редірект на /my/; блок «Мої курси»; у меню — «Student User».
+5. Сеанс завершено, відкрито сторінку входу.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -589,24 +588,25 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -614,33 +614,37 @@
           <t>TC-02</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>F-10, GUI-20</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Помилка входу при невірному паролі зі збереженням логіну та очищенням поля пароля</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Стенд відкритий; користувач не авторизований</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Помилка входу з невірним паролем: збереження логіна, очищення пароля, фокус у полі «Пароль»</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Стенд скинуто (S1). Користувач не авторизований. Chrome 130, нова сесія інкогніто.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити /login/index.php
-2. Ввести логін 'student'
-3. Ввести пароль 'WrongPassword123!'
-4. Натиснути кнопку 'Увійти'
-5. Закрити сеанс</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Залишається на /login/index.php. Червоний блок: 'Невірне ім\'я користувача або пароль...'. Логін збережено, поле пароля порожнє.</t>
+2. У поле «Ім'я входу» ввести student
+3. У поле «Пароль» ввести WrongPass_2026
+4. Натиснути кнопку «Увійти»
+5. Не натискаючи мишею, ввести з клавіатури символ x</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито форму входу.
+2. У полі відображається student.
+3. Символи пароля приховані.
+4. Залишаємось на /login/index.php; червоний блок над полями «Невірне ім'я користувача або пароль»; «Ім'я входу» зберегло student; поле «Пароль» порожнє; фокус у полі «Пароль».
+5. Символ x з'являється в полі «Пароль».</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -655,22 +659,27 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>#1 (BUG-001)</t>
         </is>
       </c>
     </row>
@@ -680,34 +689,37 @@
           <t>TC-03</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>F-10, S-20</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Блокування облікового запису на 15 хвилин після 3 послідовних невдалих спроб входу</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Стенд відкритий; лічильник спроб для 'student' дорівнює 0</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Блокування облікового запису на 15 хвилин після 3 невдалих спроб входу</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Стенд скинуто (S1). Лічильник невдалих спроб для student дорівнює 0. Chrome 130, нова сесія інкогніто.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити /login/index.php
-2. Ввести 'student' і невірний пароль 1, натиснути 'Увійти'
-3. Ввести невірний пароль 2, натиснути 'Увійти'
-4. Ввести невірний пароль 3, натиснути 'Увійти'
-5. Ввести правильний пароль 'sandbox24' і натиснути 'Увійти'
-6. Закрити браузер</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Після кроку 4 та на кроці 5 відображається повідомлення: 'Обліковий запис тимчасово заблоковано на 15 хвилин...'. Вхід блокується.</t>
+2. Ввести student і пароль WrongPass_1, натиснути «Увійти»
+3. Ввести пароль WrongPass_2, натиснути «Увійти»
+4. Ввести пароль WrongPass_3, натиснути «Увійти»
+5. Ввести правильний пароль sandbox24, натиснути «Увійти»</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито форму входу.
+2. Помилка входу, лічильник спроб — 1.
+3. Помилка входу, лічильник спроб — 2.
+4. Помилка входу; повідомлення «Обліковий запис тимчасово заблоковано на 15 хвилин»; поля форми недоступні.
+5. Вхід відхилено з тим самим повідомленням про блокування.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -717,27 +729,32 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Негативний / BVA</t>
+          <t>Негативний / BVA (3 спроби)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>#2 (BUG-002)</t>
         </is>
       </c>
     </row>
@@ -747,32 +764,35 @@
           <t>TC-04</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>F-20</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Запит на скидання пароля за валідним зареєстрованим email користувача</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Користувач не в системі; в базі існує student@example.com</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Запит на відновлення пароля за зареєстрованим email</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Стенд скинуто (S1). Акаунт student має email student@example.com. Demo не надсилає листів (SRS 1.1, п. 2.3). Firefox 131, нова сесія.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити /login/forgot_password.php
-2. У поле пошуку за email ввести 'student@example.com'
-3. Натиснути кнопку 'Знайти'
-4. Закрити сторінку</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Відображається повідомлення: 'Якщо ви вказали правильне ім\'я або адресу, на неї має бути надіслано лист... (посилання дійсне 30 хв)'.</t>
+2. У поле пошуку ввести student@example.com
+3. Натиснути кнопку «Пошук»
+4. Закрити вкладку</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито сторінку «Забули пароль?» з полем пошуку.
+2. Значення введено.
+3. Повідомлення про надсилання інструкцій на вказану пошту; лист не перевіряється, бо demo не надсилає пошту.
+4. Вкладку закрито.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -787,24 +807,25 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -812,32 +833,35 @@
           <t>TC-05</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>F-20</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Запит відновлення пароля з неіснуючим email без розкриття факту відсутності акаунту</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Користувач не в системі; nonexistent_user@domain.xyz відсутній в системі</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Відновлення пароля для неіснуючого облікового запису без розкриття його відсутності</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Стенд скинуто (S1). Користувач not_existing_student_2026 у системі відсутній. Chrome 130, нова сесія.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити /login/forgot_password.php
-2. Ввести email 'nonexistent_user@domain.xyz'
-3. Натиснути кнопку 'Знайти'
-4. Закрити сторінку</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Показується нейтральне стандартне повідомлення про відправку без помилок про неіснування запису (захист від перебору).</t>
+2. У поле пошуку ввести not_existing_student_2026
+3. Натиснути кнопку «Пошук»
+4. Закрити вкладку</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито сторінку «Забули пароль?».
+2. Значення введено.
+3. Показано нейтральне повідомлення «Якщо обліковий запис існує, інструкції надіслано на вказану пошту»; текст не підтверджує і не заперечує наявність запису.
+4. Вкладку закрито.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -852,22 +876,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>#3 (BUG-003)</t>
         </is>
       </c>
     </row>
@@ -877,32 +906,37 @@
           <t>TC-06</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>F-30</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Пошук навчального курсу в каталозі за валідним фрагментом назви</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Каталог містить курс 'Технології тестування програмного забезпечення'</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>1. Відкрити сторінку каталогу /course/index.php
-2. У поле 'Пошук курсів' ввести 'тестування'
-3. Натиснути клавішу Enter
-4. Закрити перегляд</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Каталог відфільтровано: відображається картка курсу 'Технології тестування...'; невідповідні курси приховані.</t>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Пошук курсу в каталозі за фрагментом назви без урахування регістру</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Виконано підготовку S2: створено курс «Технології тестування програмного забезпечення». Користувач не авторизований. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити /course/index.php
+2. У поле «Пошук курсів» ввести тестування
+3. Натиснути Enter
+4. Переглянути список результатів до кінця
+5. Закрити вкладку</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито каталог курсів.
+2. У полі відображається тестування.
+3. Список відфільтровано.
+4. У результатах є картка «Технології тестування програмного забезпечення»; курси без збігу приховані.
+5. Вкладку закрито.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -917,24 +951,25 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -942,32 +977,35 @@
           <t>TC-07</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>F-30</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Обробка пошуку неіснуючого курсу з виведенням повідомлення 'Жодного курсу не знайдено'</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Сторінка каталогу курсів відкрита</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Пошук курсу за рядком, що не має збігів, із повідомленням про порожній результат</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Каталог курсів доступний без входу. Chrome 130, нова сесія.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. Відкрити /course/index.php
-2. У поле 'Пошук курсів' ввести 'NonExistentCourse_XYZ_999'
-3. Натиснути клавішу Enter
+2. У поле «Пошук курсів» ввести NonExistentCourse_XYZ_999
+3. Натиснути Enter
 4. Закрити вкладку</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>У центральній панелі відображається повідомлення: 'Жодного курсу не знайдено'. Список результатів порожній.</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито каталог курсів.
+2. Значення введено.
+3. Список результатів порожній; показано повідомлення «Жодного курсу не знайдено».
+4. Вкладку закрито.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -982,24 +1020,25 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1007,33 +1046,39 @@
           <t>TC-08</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>F-40, GUI-50, BL-70</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Успішне самозарахування студента за валідним кодовим словом</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Студент student авторизований; для курсу id=2 задано кодове слово 'QA-Pass-2026'</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом ('student' / 'sandbox24')
-2. Відкрити сторінку зарахування /enrol/index.php?id=2
-3. У поле 'Кодове слово' ввести 'QA-Pass-2026'
-4. Натиснути кнопку 'Приєднатися до курсу'
-5. У меню користувача натиснути 'Вихід'</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Успішне зарахування; відкривається сторінка /course/view.php?id=2. Після кроку 5 сеанс закрито.</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Самозарахування студента за точним кодовим словом із присвоєнням ролі «Студент»</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: курс «Технології тестування ПЗ» (id=2) має самореєстрацію з кодовим словом QA-Pass-2026. Студент student авторизований, на курс ще не зарахований.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити /course/view.php?id=2
+2. Перевірити блок «Самореєстрація (Студент)»
+3. У поле «Кодове слово» ввести QA-Pass-2026
+4. Натиснути «Приєднатися до курсу»
+5. Відкрити «Учасники» і знайти student
+6. У меню користувача натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито сторінку «Параметри зарахування».
+2. Є поле «Кодове слово» (символи приховані) і кнопка «Приєднатися до курсу».
+3. Значення введено.
+4. Зараховано; відкрито /course/view.php?id=2.
+5. У списку учасників student має роль «Студент».
+6. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1048,24 +1093,25 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1073,33 +1119,37 @@
           <t>TC-09</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>F-40, GUI-60, BL-80</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Відхилення самозарахування при невірному кодовому слові з написом про помилку</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Студент авторизований; кодове слово курсу 'QA-Pass-2026'</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити сторінку зарахування /enrol/index.php?id=2
-3. Ввести помилкове слово 'qa-pass-2026' (інший регістр)
-4. Натиснути 'Приєднатися до курсу'
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Зарахування відхилено; користувач на сторінці зарахування. Червоний напис: 'Невірне кодове слово, спробуйте ще раз'. Поле очищено.</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F-40, GUI-60, BL-70</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Відхилення самозарахування при кодовому слові з іншим регістром</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: курс id=2 має кодове слово QA-Pass-2026. Студент student авторизований, на курс не зарахований.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити /course/view.php?id=2
+2. У поле «Кодове слово» ввести qa-pass-2026
+3. Натиснути «Приєднатися до курсу»
+4. Перевірити розміщення повідомлення і вміст поля
+5. У меню користувача натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито сторінку «Параметри зарахування».
+2. Значення введено.
+3. Зарахування відхилено; студент залишається на сторінці зарахування.
+4. Під полем «Кодове слово» — червоне повідомлення «Невірне кодове слово, спробуйте ще раз»; поле очищене.
+5. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1114,22 +1164,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>#4 (BUG-004)</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1194,39 @@
           <t>TC-10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>F-50, GUI-75</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Відображення секцій курсу та фіксованої верхньої навігаційної панелі</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Студент зарахований на курс id=2; курс містить 5 секцій</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити курс /course/view.php?id=2
-3. Перевірити наявність верхньої панелі та лівого індексу секцій
-4. Натиснути 'Вихід'</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Сторінка завантажена (HTTP 200, &lt;= 3 с). Відображені секції, навігаційні лінки 'На головну', 'Мої курси', меню профілю.</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>F-50, GUI-75, P-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Сторінка курсу: секції, робочий лівий індекс і верхня навігаційна панель</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Студент зарахований на курс id=2 (S2), у курсі 5 секцій. Firefox 131, нова сесія.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student / sandbox24
+2. Відкрити /course/view.php?id=2
+3. Перевірити наявність 5 секцій і лівого індексу
+4. Натиснути посилання «Секція 2» в лівому індексі
+5. Перевірити верхню панель (назва, «На головну», «Мої курси», меню користувача)
+6. Натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито /my/.
+2. Сторінка курсу завантажено (HTTP 200, до 3 с у однокористувацькому замірі).
+3. Відображено секції 1–5; лівий індекс містить посилання на кожну секцію.
+4. Сторінка прокручена до секції 2.
+5. Усі елементи верхньої панелі присутні та клікабельні.
+6. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1179,24 +1241,25 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1204,34 +1267,39 @@
           <t>TC-11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>F-60, GUI-30</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Здача звіту завдання у форматі .pdf розміром 2.5 МБ до настання дедлайну</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Студент авторизований; дедлайн спливає через 2 дні; файл report.pdf підготовлено</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити завдання /mod/assign/view.php?id=10
-3. Натиснути 'Додати роботу'
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Здача завдання файлом report.pdf до дедлайну зі зміною статусу</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: завдання «Лабораторна робота 1» (id=10) з дедлайном +2 доби, дозволені .pdf/.docx/.zip/.java, до 20 МБ, до 5 файлів. Студент зарахований, файл report.pdf (2.5 МБ) підготовлено.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student / sandbox24
+2. Відкрити /mod/assign/view.php?id=10
+3. Натиснути «Додати роботу»
 4. Завантажити report.pdf (2.5 МБ)
-5. Натиснути 'Зберегти зміни'
-6. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Статус змінено на 'Здано для оцінювання' (зелений фон). Зафіксовано дату/час; напис про запізнення відсутній.</t>
+5. Натиснути «Зберегти зміни»
+6. Перевірити статус і дату здачі</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито /my/.
+2. Сторінка завдання з кнопкою «Додати роботу».
+3. Відкрито форму з областю «Файли» та редактором «Онлайн-текст».
+4. Файл report.pdf відображається у списку вкладень.
+5. Зміни збережено без повідомлень про помилку.
+6. Статус «Здано для оцінювання», зафіксовано дату й час; позначки про запізнення немає.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1246,24 +1314,25 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1271,32 +1340,37 @@
           <t>TC-12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>F-60, GUI-30</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Блокування завантаження файлу недозволеного формату (.exe) при здачі завдання</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Студент на формі здачі практичної роботи; підготовлено файл script.exe</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити форму здачі /mod/assign/view.php?id=10&amp;action=editsubmission
-3. Спробувати завантажити script.exe
-4. Натиснути 'Скасувати' та вийти</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Завантаження заблоковано. Повідомлення: 'Файли типу .exe не приймаються. Дозволені типи: .pdf, .docx, .zip, .java'.</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GUI-30, F-60</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Блокування завантаження файлу .exe у формі здачі завдання</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: завдання id=10 дозволяє лише .pdf/.docx/.zip/.java. Студент авторизований; підготовлено solution.exe (250 КБ).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити /mod/assign/view.php?id=10
+2. Натиснути «Додати роботу»
+3. Додати файл solution.exe
+4. Натиснути «Зберегти зміни»
+5. Перевірити статус завдання</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Сторінка завдання відкрита.
+2. Відкрито форму здачі.
+3. Файл не додано; показано повідомлення «Файли типу .exe не дозволені. Допустимі розширення: .pdf, .docx, .zip, .java».
+4. Збереження не відбувається; форма залишається відкритою.
+5. Статус залишається «Чернетка»; робота не вважається зданою.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1311,22 +1385,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>#5 (BUG-005)</t>
         </is>
       </c>
     </row>
@@ -1336,33 +1415,37 @@
           <t>TC-13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>GUI-30</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка розміру прикріплюваного файлу на межі 20 МБ (20.00 МБ vs 20.01 МБ)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Студент на формі здачі; підготовлено file_20mb.zip (20.00 МБ) та file_20_01mb.zip (20.01 МБ)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом, відкрити форму здачі завдання
-2. Додати file_20mb.zip (20.00 МБ)
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Граничний розмір файлу: 20.00 МБ приймається, 20.01 МБ відхиляється</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Форма здачі завдання id=10 відкрита; підготовлено file_20mb.zip (20.00 МБ) і file_20_01mb.zip (20.01 МБ). Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити форму здачі завдання
+2. Додати file_20mb.zip (20.00 МБ) — верхня межа b
 3. Видалити доданий файл
-4. Додати file_20_01mb.zip (20.01 МБ)
-5. Натиснути 'Скасувати' та вийти</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Файл 20.00 МБ успішно додається. Файл 20.01 МБ відхиляється: 'Файл завеликий. Максимальний дозволений розмір — 20 МБ'.</t>
+4. Додати file_20_01mb.zip (20.01 МБ) — b+1
+5. Натиснути «Скасувати»</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Форма здачі відкрита.
+2. Файл 20.00 МБ додано без помилки.
+3. Список вкладень порожній.
+4. Файл відхилено; повідомлення «Файл завеликий. Максимальний дозволений розмір — 20 МБ».
+5. Форму закрито без збереження.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1377,24 +1460,25 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1402,32 +1486,37 @@
           <t>TC-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>GUI-30</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка кількості файлів у відповіді (5 шт. дозволено vs 6 шт. блокується)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Студент на формі здачі; підготовлено 6 файлів .pdf по 100 КБ</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом, відкрити форму здачі
-2. Завантажити файли 1, 2, 3, 4, 5 (разом 5 шт.)
-3. Спробувати завантажити 6-й файл
-4. Натиснути 'Скасувати' та вийти</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>5 файлів успішно розміщено. Додавання 6-го блокується: 'Ви не можете завантажити більше ніж 5 файлів на одне завдання'.</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Гранична кількість файлів: 5 приймаються, 6-й блокується</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Форма здачі завдання id=10 відкрита; підготовлено 6 файлів .pdf по 100 КБ. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити форму здачі
+2. Додати файли lab1_p1.pdf … lab1_p5.pdf (5 шт.)
+3. Спробувати додати lab1_p6.pdf (6-й файл)
+4. Перевірити список вкладень
+5. Натиснути «Скасувати»</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Форма здачі відкрита.
+2. 5 файлів додано (b = 5).
+3. 6-й файл не додано; повідомлення «Дозволено завантажувати не більше 5 файлів».
+4. У списку рівно 5 файлів.
+5. Форму закрито без збереження.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,22 +1531,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>#6 (BUG-006)</t>
         </is>
       </c>
     </row>
@@ -1467,33 +1561,39 @@
           <t>TC-15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>F-60, BL-30</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Автоматичне нарахування штрафу 10% за 1 день запізнення здачі роботи</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Робота здана на 1 день пізніше дедлайну; викладач оцінює на 100 балів</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти викладачем ('teacher' / 'sandbox24')
-2. Відкрити оцінювання запізнілої роботи студента
-3. Ввести оцінку 100 балів і зберегти
-4. Переглянути підсумковий рядок у журналі
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Модуль GradeCalculator.latePenalty нараховує -10.0%. Зарахований бал = 90.00 б. Позначено: 'Штраф (1 день): -10%'.</t>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Штраф 10% за здачу на один день пізніше дедлайну</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: завдання «Лабораторна робота 2» (id=11) з дедлайном учора 23:59; student зарахований; викладач teacher / sandbox24.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як teacher і відкрити /mod/assign/view.php?id=11
+2. Перевірити, що дедлайн встановлено на вчора 23:59
+3. Увійти як student і здати report_late.pdf
+4. Увійти як teacher і відкрити «Переглянути всі роботи»
+5. Виставити оцінку 100 і зберегти
+6. Відкрити журнал оцінок і перевірити підсумок за завдання</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Сторінка завдання відкрита.
+2. Дедлайн — попередній день, 23:59.
+3. Роботу здано; статус «Здано для оцінювання».
+4. Відкрито список робіт студента.
+5. Оцінку 100 збережено.
+6. Підсумок 90.00; позначка «Штраф (1 день): -10%».</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1508,22 +1608,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>#7 (BUG-007)</t>
         </is>
       </c>
     </row>
@@ -1533,33 +1638,37 @@
           <t>TC-16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>F-60, BL-30</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Фіксація штрафу на максимальному ліміті 50% при запізненні на 5 і 6 днів (penalty cap)</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Оцінюються 2 роботи: запізнення 5 днів (студент А) та 6 днів (студент Б); бали по 100 б.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти викладачем
-2. Оцінити студента А (5 днів запізнення) на 100 б.
-3. Оцінити студента Б (6 днів запізнення) на 100 б.
-4. Перевірити журнал оцінок
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Студент А: штраф 50%, підсумок = 50.00 б. Студент Б: штраф також 50% (не 60%), підсумок = 50.00 б. Ліміт 50% дотримано.</t>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Обмеження штрафу 50% при запізненні на 5 і 6 днів</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: завдання «Лабораторна 5» (id=12) з дедлайном 5 днів тому і «Лабораторна 6» (id=13) з дедлайном 6 днів тому; student зарахований.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і здати report_5d.pdf у завдання id=12
+2. Здати report_6d.pdf у завдання id=13
+3. Увійти як teacher і виставити 100 балів за обидва завдання
+4. Відкрити журнал оцінок
+5. Перевірити підсумки за обома завданнями</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Роботу здано із запізненням 5 днів.
+2. Роботу здано із запізненням 6 днів.
+3. Обидві оцінки 100 збережено.
+4. Журнал оцінок відкрито.
+5. Обидва підсумки 50.00; штраф 50% (не 60%) для обох робіт.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1574,24 +1683,25 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1599,33 +1709,39 @@
           <t>TC-17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>F-70</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Оцінювання завдання викладачем із виставленням балу та внесенням коментаря</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Студент здав роботу вчасно; викладач у розділі оцінювання</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти викладачем
-2. Відкрити форму оцінювання студента /mod/assign/view.php?id=10&amp;action=grader
-3. Ввести оцінку '95' і відгук 'Відмінна робота!'
-4. Натиснути 'Зберегти зміни'
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Оцінку 95.00 та відгук збережено. У кабінеті студента статус стає 'Оцінено', бал '95.00 / 100.00', відгук відображається.</t>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Оцінювання роботи викладачем із балом і текстовим відгуком</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Студент здав «Лабораторну роботу 1» (TC-11). Викладач teacher авторизований. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити /mod/assign/view.php?id=10&amp;action=grading
+2. Обрати роботу student
+3. Ввести оцінку 95
+4. Ввести відгук «Відмінна робота!» і натиснути «Зберегти зміни»
+5. Увійти як student і відкрити сторінку завдання
+6. Натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито таблицю оцінювання.
+2. Відкрито форму оцінювання student.
+3. У полі «Оцінка» — 95.
+4. Оцінку і відгук збережено.
+5. Студент бачить «95.00 / 100.00» і відгук «Відмінна робота!».
+6. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1640,24 +1756,25 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1665,34 +1782,43 @@
           <t>TC-18</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>F-80, GUI-40, BL-60</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Успішне проходження тесту студентом із наданням відповідей та авторозрахунком</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Студент відкрив тест 'Модульний контроль 1'; таймер 15 хв</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити тест /mod/quiz/view.php?id=15
-3. Натиснути 'Спроба тесту'
-4. Відповісти на питання 1 та 2 (правильні варіанти)
-5. Натиснути 'Завершити спробу…' -&gt; 'Надіслати все і завершити'
-6. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Сторінка огляду спроби: стан 'Завершено', оцінка '100.00%'. Плитки питань навігації пофарбовані сірим кольором.</t>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Проходження тесту з переходом між питаннями та автоматичним підрахунком</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: тест «Модульний контроль 1» (id=15) має 2 питання, ліміт 3 спроби, таймер 15 хв. Студент зарахований.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити /mod/quiz/view.php?id=15
+2. Натиснути «Спроба тесту»
+3. Відповісти на питання 1 (правильний варіант)
+4. Перейти на питання 2 через плитку навігації
+5. Відповісти на питання 2 (правильні варіанти)
+6. Повернутися на питання 1 і перевірити збереження відповіді
+7. Натиснути «Завершити спробу…» → «Надіслати все і завершити»
+8. Перевірити сторінку огляду спроби</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито сторінку тесту з кнопкою «Спроба тесту».
+2. Відкрито питання 1; праворуч — плитки 1, 2 і таймер.
+3. Відповідь позначено; плитка 1 змінила колір.
+4. Відкрито питання 2.
+5. Відповіді позначено; плитка 2 змінила колір.
+6. Відповідь на питання 1 збережена.
+7. Спроба завершена.
+8. Стан «Завершено», оцінка «100.00%», обидві плитки сірі.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1707,24 +1833,25 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1732,34 +1859,43 @@
           <t>TC-19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>F-80</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Граничний контроль ліміту спроб тесту (3 дозволені спроби vs 4-та заблокована)</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Ліміт тесту: 3 спроби. Студент завершив 2 спроби (бали 60% та 75%)</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом, відкрити сторінку тесту
-2. Натиснути 'Пройти тест знову' (спроба 3 з 3)
-3. Скласти тест на 85%, завершити і надіслати
-4. Повернутися на сторінку тесту
-5. Перевірити стан кнопки спроби
-6. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Після 3-ї спроби кнопка початку неактивна або відсутня; напис: 'Більше спроб не дозволено'. Зараховано найвищу оцінку 85.0%.</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Ліміт 3 спроби тесту: четверта спроба недоступна</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: тест id=15 має ліміт 3 спроби. Студент зарахований, у поточному прогоні спроб не має. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити /mod/quiz/view.php?id=15
+2. Пройти спробу 1 і надіслати відповіді
+3. Повернутися на сторінку тесту
+4. Пройти спробу 2 і надіслати відповіді
+5. Повернутися на сторінку тесту
+6. Пройти спробу 3 і надіслати відповіді
+7. Повернутися на сторінку тесту і перевірити блок спроб
+8. Спробувати розпочати спробу 4</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Доступна кнопка «Спроба тесту».
+2. Спроба 1 завершена; показано результат.
+3. На сторінці тесту «Спроб: 1 з 3».
+4. Спроба 2 завершена.
+5. На сторінці тесту «Спроб: 2 з 3».
+6. Спроба 3 завершена.
+7. Кнопки початку немає; напис «Більше спроб не дозволено»; «Спроб: 3 з 3».
+8. Спроба не починається.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1774,22 +1910,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>#8 (BUG-008)</t>
         </is>
       </c>
     </row>
@@ -1799,33 +1940,37 @@
           <t>TC-20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>F-80, BL-50</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Завершення спроби тесту без вибору варіантів (Порожній стан selected == null)</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Студент розпочав спробу тестування; відповіді не обрано</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом, відкрити спробу тесту
-2. Не обирати жодного варіанта у питаннях
-3. Натиснути 'Завершити спробу…'
-4. Підтвердити 'Надіслати все і завершити'
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Спроба зареєстрована; оцінка: '0.00 з 10.00 (0.0%)'. Система коректно обробляє порожній вибір без винятків.</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>F-80, BL-40</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Завершення спроби тесту без жодної відповіді</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Тест id=15 має 2 питання; студент має доступну спробу. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити спробу тесту
+2. Не обирати жодного варіанта
+3. Натиснути «Завершити спробу…»
+4. Підтвердити «Надіслати все і завершити»
+5. Перевірити оцінку</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Спроба відкрита.
+2. Питання без відповідей.
+3. Відкрито підтвердження завершення.
+4. Спроба зареєстрована без помилки.
+5. Оцінка «0.00 з 2.00 (0.0%)».</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1840,24 +1985,25 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1865,33 +2011,37 @@
           <t>TC-21</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>F-80, BL-50</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Нарахування часткового балу в тесті з вибором 1 правильного варіанта з 2</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Питання містить 2 правильні та 2 неправильні відповіді; макс. бал = 1.0</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом, відкрити спробу тесту
-2. У питанні обрати прапорець варіанта A (1 правильний з 2) і не обирати інші
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Частковий бал за питання з кількома правильними відповідями</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Питання 2 тесту id=15 має 4 варіанти, з них 2 правильні; максимум 1.0 бала. Студент має доступну спробу. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і розпочати спробу
+2. У питанні 2 обрати лише один правильний варіант
 3. Завершити спробу та надіслати відповіді
-4. Переглянути оцінку за питання
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>За формулою (1/2 - 0/2) * 1.0 нараховано рівно 0.5 бала (50%). При виборі помилкових варіантів бал не опускається нижче 0.0.</t>
+4. Відкрити огляд спроби
+5. Перевірити бал за питання 2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Спроба відкрита.
+2. Обрано 1 із 2 правильних варіантів.
+3. Спроба завершена.
+4. Відкрито огляд спроби.
+5. Бал за питання 2 — 0.50 з 1.00; від'ємного бала немає.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1901,29 +2051,30 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Позитивний / Частковий бал</t>
+          <t>Позитивний / частковий бал</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1931,34 +2082,41 @@
           <t>TC-22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>F-90, GUI-80</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Створення нової теми для обговорення на форумі курсу викладачем</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Викладач авторизований; відкрита сторінка форуму</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти викладачем
-2. Відкрити форум курсу /mod/forum/view.php?id=20
-3. Натиснути 'Додати нову тему для обговорення'
-4. Заповнити 'Тема': 'Розклад консультацій', 'Повідомлення': 'Консультація о 16:00'
-5. Натиснути 'Опублікувати на форумі'
-6. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Зелене повідомлення про успішне створення. У таблиці форуму з'являється рядок теми з автором 'Teacher Terri'.</t>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Створення викладачем нової теми форуму та доступність редагування автором</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: форум «Новини курсу» (id=20) існує; teacher зарахований як викладач. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як teacher і відкрити /mod/forum/view.php?id=20
+2. Натиснути «Додати нову тему для обговорення»
+3. Заповнити «Тема»: Розклад консультацій
+4. Заповнити «Повідомлення»: Консультація о 16:00
+5. Натиснути «Опублікувати на форумі»
+6. Перевірити рядок теми та посилання «Редагувати»
+7. Натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито форум курсу.
+2. Відкрито форму нової теми.
+3. У полі «Тема» — введений текст.
+4. У редакторі — введений текст.
+5. Показано повідомлення про успішне створення.
+6. Тема є в таблиці форуму, автор — «Teacher Terri»; для автора доступне посилання «Редагувати».
+7. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1973,24 +2131,25 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1998,33 +2157,37 @@
           <t>TC-23</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>GUI-80</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Блокування публікації теми форуму при порожньому обов'язковому полі 'Тема'</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Викладач на формі створення теми форуму</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти викладачем, відкрити форму створення теми
-2. Поле 'Тема' залишити порожнім
-3. У поле 'Повідомлення' ввести текст
-4. Натиснути 'Опублікувати на форумі'
-5. Натиснути 'Скасувати' та вийти</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Форма не відправляється; біля поля 'Тема' з'являється червоний напис 'Обов\'язкове поле' (або браузерне сповіщення).</t>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Блокування публікації теми форуму з порожнім полем «Тема»</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Викладач авторизований; відкрито форму створення теми форуму. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити форму «Додати нову тему для обговорення»
+2. Залишити поле «Тема» порожнім
+3. У поле «Повідомлення» ввести Перевірка валідації
+4. Натиснути «Опублікувати на форумі»
+5. Перевірити список тем</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Форма відкрита.
+2. Поле «Тема» порожнє.
+3. Повідомлення введено.
+4. Форма не надсилається; поле «Тема» підсвічене червоним; показано підказку «Заповніть це поле».
+5. Нова тема у списку відсутня.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2039,24 +2202,25 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2064,33 +2228,39 @@
           <t>TC-24</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>F-90</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Автоматичне маркування повідомлення форуму зі стоп-словом як 'Потребує модерації'</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Словник стоп-слів містить тестове слово '[toxic_word]'</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. Відкрити гілку форуму та натиснути 'Відповісти'
-3. Ввести текст зі стоп-словом: 'Текст [toxic_word] перевірка'
-4. Натиснути 'Опублікувати на форумі'
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Повідомлення приховано від одногрупників та позначено системним маркером 'Потребує модерації' для викладача.</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Маркування повідомлення форуму зі стоп-словом для перевірки викладачем</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S5: адміністратор додав слово «спойлер» до словника стоп-слов. Студент зарахований на курс, форум id=20 доступний. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student і відкрити тему форуму
+2. Натиснути «Відповісти»
+3. Ввести текст «У цьому пості є спойлер до фіналу.»
+4. Натиснути «Опублікувати на форумі»
+5. Перевірити вигляд повідомлення у студента
+6. Увійти як teacher і перевірити маркування</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Тему форуму відкрито.
+2. Відкрито форму відповіді.
+3. Текст введено.
+4. Повідомлення опубліковано.
+5. Повідомлення приховане від інших студентів до рішення викладача.
+6. У викладача повідомлення позначене «Потребує перевірки».</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2100,27 +2270,32 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Негативний / Модерація</t>
+          <t>Негативний / модерація</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>#9 (BUG-009)</t>
         </is>
       </c>
     </row>
@@ -2130,32 +2305,37 @@
           <t>TC-25</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>F-100, GUI-45</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Перегляд персонального журналу оцінок студентом з літерою ECTS</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Студент зарахований; виставлено оцінки; розрахунковий підсумок 88.50 балів</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти студентом
-2. У меню користувача натиснути 'Оцінки'
-3. Перевірити наявність колонок GUI-45 та фінального рядка
-4. Натиснути 'Вихід'</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Відкривається таблиця оцінок. Підсумковий рядок містить бал '88.50' та літеру ECTS 'B' (відповідно до 85.00..94.99).</t>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Журнал оцінок студента: стовпці, підсумок і літера ECTS</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: student має оцінки 95 і 82 за двома рівноваговими елементами (підсумок 88.50). Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student
+2. У меню користувача натиснути «Оцінки»
+3. Перевірити склад стовпців таблиці
+4. Перевірити підсумковий рядок і літеру ECTS
+5. Натиснути «Вихід»</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито /my/.
+2. Відкрито сторінку «Оцінки» курсу.
+3. Присутні стовпці «Елемент оцінювання», «Розрахована вага», «Оцінка», «Діапазон», «Відсоток», «Відгук», «Внесок у підсумок» і стовпець «ECTS».
+4. Підсумок 88.50 виділено жирним; літера ECTS — B (85.00 ≤ 88.50 &lt; 95.00).
+5. Сеанс завершено.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2170,22 +2350,27 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>#10 (BUG-010)</t>
         </is>
       </c>
     </row>
@@ -2195,32 +2380,37 @@
           <t>TC-26</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>BL-20</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Гранична верифікація шкали ECTS на стику літер Fx та E (59.99 б. vs 60.00 б.)</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Доступний модуль GradeCalculator.ectsLetter(total)</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>1. Викликати GradeCalculator.ectsLetter(59.99)
-2. Зафіксувати результат літери
-3. Викликати GradeCalculator.ectsLetter(60.00)
-4. Зафіксувати результат літери</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Для total = 59.99 метод повертає 'Fx'. Для total = 60.00 метод повертає 'E'. Межа неперервного інтервалу дотримана.</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>F-100, BL-20</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Межа шкали ECTS Fx/E у журналі оцінок: 59.99 і 60.00</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: курс id=2 має один елемент оцінювання з вагою 100%; student зарахований, викладач може перевизначити підсумок курсу.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як teacher і відкрити журнал оцінок курсу
+2. Встановити перевизначення підсумку курсу 59.99 і зберегти
+3. Увійти як student, відкрити «Оцінки» і знайти літеру ECTS
+4. Увійти як teacher і змінити перевизначення на 60.00
+5. Увійти як student і перевірити літеру ECTS</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Журнал оцінок відкрито.
+2. Підсумок курсу — 59.99.
+3. Літера ECTS — Fx (35.00 ≤ 59.99 &lt; 60.00).
+4. Підсумок курсу — 60.00.
+5. Літера ECTS — E (60.00 ≤ 60.00 &lt; 65.00).</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2235,24 +2425,25 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2260,63 +2451,72 @@
           <t>TC-27</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>BL-20</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Гранична верифікація шкали ECTS на стику літер B та A (94.99 б. vs 95.00 б.)</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Доступний модуль GradeCalculator.ectsLetter(total)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>1. Викликати GradeCalculator.ectsLetter(94.99)
-2. Викликати GradeCalculator.ectsLetter(95.00)
-3. Викликати GradeCalculator.ectsLetter(100.01)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Для 94.99 повертається 'B'. Для 95.00 повертається 'A'. Для 100.01 генерується IllegalArgumentException.</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>F-110</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Редагування профілю студента та модерація зміни ПІБ</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Студент student авторизований. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити меню користувача → «Профіль» → «Редагувати інформацію»
+2. Змінити «Місто» на Київ і «Опис» на Студент ФБ-44
+3. Натиснути «Оновити профіль»
+4. Перезавантажити сторінку профілю
+5. Змінити «Прізвище» на Шевченко і натиснути «Оновити профіль»
+6. Перевірити повідомлення та значення прізвища</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито форму редагування профілю.
+2. Поля містять введені значення.
+3. Зміни збережено.
+4. У профілі відображаються Київ і «Студент ФБ-44».
+5. Показано повідомлення «Зміну ПІБ надіслано на модерацію».
+6. У профілі залишається попереднє прізвище до підтвердження уповноваженою особою.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Граничний (BVA)</t>
+          <t>Позитивний</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2324,63 +2524,74 @@
           <t>TC-28</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>BL-10</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Граничний контроль суми ваг оцінюваних елементів курсу (99.9% vs 100.0% vs 100.1%)</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Доступний метод GradeCalculator.weightedTotal(items)</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1. Передати елементи з сумою ваг 99.9%
-2. Передати елементи з сумою ваг 100.0% (бали по 80.0)
-3. Передати елементи з сумою ваг 100.1%</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Кроки 1 та 3 генерують IllegalArgumentException('Total weight must be 100%'). Крок 2 обчислює підсумок 80.00 балів.</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>F-120</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Календар: події дедлайнів курсу та створення особистої події</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S2: завдання id=10 має дедлайн +2 доби, тест id=15 закривається через 3 доби. Студент зарахований. Firefox 131.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1. Увійти як student
+2. Відкрити «Календар» у поданні «Місяць»
+3. Перевірити події дедлайну завдання і закриття тесту
+4. Натиснути «Нова подія»
+5. Заповнити назву «Консультація», дату — завтра, час 16:00, тривалість 60 хв
+6. Натиснути «Зберегти»
+7. Перевірити появу події в календарі</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито /my/.
+2. Відкрито календар у поданні «Місяць».
+3. У відповідні дні є події «Лабораторна робота 1» і «Модульний контроль 1».
+4. Відкрито форму нової події.
+5. Поля заповнено.
+6. Подію збережено.
+7. Подія «Консультація» відображається на завтра о 16:00.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Граничний (BVA)</t>
+          <t>Позитивний</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2388,62 +2599,70 @@
           <t>TC-29</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BL-70, BL-80</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Блокування зарахування при нескладеному пререквізиті (бал &lt; 60) з кодом ERR_PREREQUISITE</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Студент має бал за передумовний курс 59.90 б. (&lt; 60.0); ключ і період валідні</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>1. Викликати EnrollmentValidator.canEnroll(...)
-2. Викликати EnrollmentValidator.violations(...)</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>canEnroll повертає false. violations повертає список: ['ERR_PREREQUISITE: Пререквізит не виконано (бал &lt; 60)'].</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GUI-70, GUI-90</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Адаптивне подання календаря на 375 px і кросбраузерність Chrome/Firefox</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Студент авторизований; Chrome 130 і Firefox 131; календар містить події з TC-28. Desktop 1920×1080 і емуляція 375×812.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. У Chrome відкрити календар на 1920×1080
+2. У Chrome DevTools увімкнути 375×812 і перевірити подання
+3. Перевірити горизонтальну прокрутку та розмір тач-таргетів
+4. Повторити кроки 1–3 у Firefox 131 на ширині 375 px
+5. Закрити обидва браузери</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Доступні подання «Місяць», «День», «Наступні події», кнопки переходу між місяцями та «Нова подія».
+2. Календар переходить у мобільне подання зі списком подій.
+3. Горизонтальної прокрутки немає; кнопки й дати не менші за 44×44 px.
+4. У Firefox відображення і поведінка ідентичні Chrome; горизонтальної прокрутки немає.
+5. Браузери закрито.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Негативний</t>
+          <t>Позитивний</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2451,33 +2670,37 @@
           <t>TC-30</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>F-130</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Заборона реєстрації курсу менеджером при дублюванні існуючої короткої назви курсу</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Менеджер авторизований; у системі вже існує курс із короткою назвою 'QA-2026'</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>1. Увійти менеджером ('manager' / 'sandbox24')
-2. Відкрити 'Керування сайтом' -&gt; 'Курси' -&gt; 'Додати новий курс'
-3. Ввести повну назву 'Новий курс' та коротку назву 'QA-2026'
-4. Натиснути 'Зберегти та показати'
-5. Вийти з системи</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Створення блокується. Червоне повідомлення: 'Ця коротка назва курсу вже використовується для іншого курсу. Вкажіть унікальну назву'.</t>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Заборона створення курсу з дубльованою короткою назвою</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Виконано S3: курс із короткою назвою QA-2026 існує. Менеджер manager / sandbox24 авторизований. Chrome 130.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити «Керування сайтом» → «Курси» → «Додати новий курс»
+2. Ввести повну назву «Новий курс»
+3. Ввести коротку назву QA-2026
+4. Натиснути «Зберегти та показати»
+5. Перевірити список курсів</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрито форму створення курсу.
+2. Повну назву введено.
+3. Коротку назву введено.
+4. Створення заблоковано; повідомлення «Ця коротка назва курсу вже використовується для іншого курсу. Вкажіть унікальну назву».
+5. Курс «Новий курс» у списку відсутній.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2492,26 +2715,28 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Костенко В.</t>
+          <t>Костенко В. (Тест-аналітик)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О.</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reviewed ✓</t>
-        </is>
-      </c>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2525,14 +2750,14 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID вимоги</t>
@@ -2540,12 +2765,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Формулювання вимоги SRS 1.1</t>
+          <t>Формулювання (скорочено)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Прив'язані тест-кейси (TC)</t>
+          <t>TC-… / Issue</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2555,7 +2780,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Примітка та техніка перевірки</t>
+          <t>Примітка</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2790,12 @@
           <t>F-10</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Форма входу, створення сеансу, реакція на помилки, блокування на 15 хв після 3 спроб</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Форма входу, сесія, помилки, блокування після 3 спроб</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TC-01, TC-02, TC-03</t>
         </is>
@@ -2580,9 +2805,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Позитивний вхід, невірний пароль, блокування</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Позитивний вхід, негативний пароль, BVA блокування</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2817,12 @@
           <t>F-20</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Відновлення пароля за email/логіном, безпечне повідомлення при неіснуючому email</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Відновлення пароля, нейтральне повідомлення</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>TC-04, TC-05</t>
         </is>
@@ -2607,9 +2832,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Валідний email та захист від перебору</t>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Наявний і неіснуючий запис; лист не надсилається demo</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2844,12 @@
           <t>F-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Публічний каталог курсів, пошук без урахування регістру, повідомлення про відсутність</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Каталог курсів і пошук без урахування регістру</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>TC-06, TC-07</t>
         </is>
@@ -2634,9 +2859,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Позитивний пошук та обробка відсутності збігів</t>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Позитивний пошук і порожній результат</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2871,12 @@
           <t>F-40</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Самозарахування на курс за кодовим словом з урахуванням регістру</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Самозарахування за кодовим словом</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>TC-08, TC-09</t>
         </is>
@@ -2661,9 +2886,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Точний збіг ключа та помилка регістру</t>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Точний збіг і хибний регістр</t>
         </is>
       </c>
     </row>
@@ -2673,12 +2898,12 @@
           <t>F-50</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Сторінка курсу: навчальні секції, лівий індекс, ліміти до 50 секцій і 200 елементів</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Сторінка курсу: секції, індекс, навігація</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>TC-10</t>
         </is>
@@ -2688,9 +2913,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Завантаження сторінки курсу, навігація, P-10</t>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5 секцій, робочі посилання; P-10 — однокористувацький замір</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2925,12 @@
           <t>F-60</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Здача практичного завдання: завантаження файлів, штраф 10%/день (макс. 50%)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Здача завдання, формати, ліміти, штраф за запізнення</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>TC-11, TC-12, TC-13, TC-14, TC-15, TC-16</t>
         </is>
@@ -2715,9 +2940,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Формати файлів, ліміти 20 МБ/5 шт, штрафи</t>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Позитивна здача, .exe, межі 20 МБ / 5 файлів, штраф і ліміт 50%</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2952,12 @@
           <t>F-70</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Оцінювання викладачем: введення балу 0..100, текстовий відгук, відображення</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Оцінювання викладачем із відгуком</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>TC-17</t>
         </is>
@@ -2742,9 +2967,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Виставлення балу 95 і відгуку</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Бал 95 і відгук видимі студенту</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2979,12 @@
           <t>F-80</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Проходження тесту: навігація, таймер, до 3 спроб, вибір найвищої оцінки</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Проходження тесту, 3 спроби, найвища оцінка</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>TC-18, TC-19, TC-20, TC-21</t>
         </is>
@@ -2769,9 +2994,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Повне проходження, ліміт 3 спроб, порожній вибір</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Навігація, ліміт спроб, порожня спроба, частковий бал</t>
         </is>
       </c>
     </row>
@@ -2781,12 +3006,12 @@
           <t>F-90</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Форум курсу: створення теми, редагування 30 хв, перевірка на стоп-слова</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Форум: теми, редагування, стоп-слова</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>TC-22, TC-23, TC-24</t>
         </is>
@@ -2796,9 +3021,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Створення теми, валідація поля, маркування стоп-слів</t>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Створення теми, валідація поля, модерація</t>
         </is>
       </c>
     </row>
@@ -2808,14 +3033,14 @@
           <t>F-100</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Перегляд журналу оцінок студентом і викладачем, ручне перевизначення</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>TC-25</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Журнал оцінок, підсумок, ECTS, перевизначення</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TC-25, TC-26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2823,9 +3048,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Перегляд таблиці успішності та ECTS</t>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Стовпці й ECTS; межа Fx/E (TC-26 blocked)</t>
         </is>
       </c>
     </row>
@@ -2835,24 +3060,24 @@
           <t>F-110</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Редагування профілю: місто, опис, фото, підтвердження ПІБ деканатом</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>TC-01 (базовий профіль)</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Профіль: дані, фото, модерація ПІБ</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TC-27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Охоплено в межах перевірки меню профілю</t>
+          <t>Покрито повністю</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Місто/опис зберігаються; зміна ПІБ — на модерації</t>
         </is>
       </c>
     </row>
@@ -2862,24 +3087,24 @@
           <t>F-120</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Календар подій: дедлайни завдань, закриття тестів, особисті події</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>TC-11 (дедлайн у календарі)</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Календар: дедлайни курсу й особисті події</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TC-28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Терміни здачі фіксуються в системі</t>
+          <t>Покрито повністю</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Події завдання/тесту і створення особистої події</t>
         </is>
       </c>
     </row>
@@ -2889,12 +3114,12 @@
           <t>F-130</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Створення курсів менеджером: унікальна коротка назва, блокування дублікатів</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Створення курсів, унікальна коротка назва</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>TC-30</t>
         </is>
@@ -2904,9 +3129,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Блокування дублювання короткої назви</t>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Дубль QA-2026 блокується</t>
         </is>
       </c>
     </row>
@@ -2916,12 +3141,12 @@
           <t>GUI-10</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Форма автентифікації: поля входу, пароль, 'Забули пароль?', український інтерфейс</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Форма входу: поля, посилання, кнопки</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>TC-01, TC-02</t>
         </is>
@@ -2931,9 +3156,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Перевірено всі обов'язкові поля форми входу</t>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Склад форми і стани полів</t>
         </is>
       </c>
     </row>
@@ -2943,12 +3168,12 @@
           <t>GUI-20</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Повідомлення про помилку входу: червоний блок над полями, очищення пароля</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Повідомлення про помилку входу, фокус</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>TC-02</t>
         </is>
@@ -2958,9 +3183,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Червоний блок, фокус курсору</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Червоний блок, збереження логіна, фокус (BUG-001)</t>
         </is>
       </c>
     </row>
@@ -2970,12 +3195,12 @@
           <t>GUI-30</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Форма здачі завдання: drag-drop, .pdf/.docx/.zip/.java, до 20 МБ, до 5 файлів</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Форма здачі: формати, 20 МБ, 5 файлів</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>TC-11, TC-12, TC-13, TC-14</t>
         </is>
@@ -2985,9 +3210,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Граничні розміри 20 МБ та кількість 5 шт.</t>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Позитивна здача і три негативні/граничні перевірки</t>
         </is>
       </c>
     </row>
@@ -2997,12 +3222,12 @@
           <t>GUI-40</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Навігація тесту: плитки номерів питань, таймер зворотного відліку</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Навігація тесту: плитки питань і таймер</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>TC-18</t>
         </is>
@@ -3012,9 +3237,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Плитки питань і плаваючий таймер</t>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Перехід між питаннями, кольори плиток, таймер</t>
         </is>
       </c>
     </row>
@@ -3024,14 +3249,14 @@
           <t>GUI-45</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Таблиця журналу оцінок: 7 обов'язкових стовпців, напівжирний підсумок, ECTS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>TC-25</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Таблиця журналу оцінок, 7 стовпців, ECTS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>TC-25, TC-26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3039,9 +3264,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Стовпці, вага, внесок, літера ECTS</t>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Стовпці, жирний підсумок, ECTS (BUG-010)</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3276,12 @@
           <t>GUI-50</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Сторінка самозарахування: назва методу, поле кодового слова, кнопка</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Сторінка самозарахування</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>TC-08</t>
         </is>
@@ -3066,9 +3291,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Форма самореєстрації студента</t>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Назва методу, поле ключа, кнопка</t>
         </is>
       </c>
     </row>
@@ -3078,12 +3303,12 @@
           <t>GUI-60</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Помилка кодового слова: червоний напис під полем, очищення поля</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Помилка кодового слова під полем</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>TC-09</t>
         </is>
@@ -3093,9 +3318,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Червоне повідомлення 'Невірне кодове слово...'</t>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Місце повідомлення і очищення поля (BUG-004)</t>
         </is>
       </c>
     </row>
@@ -3105,24 +3330,24 @@
           <t>GUI-70</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Адаптивність календаря: мобільний вигляд 375..768 px, кліки &gt;= 44x44 px</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>TC-10 (responsive check)</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Мобільний календар 375–768 px</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TC-29</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Перевірено в адаптивній розмітці</t>
+          <t>Покрито повністю</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Мобільний список, без прокрутки, тач-таргети 44×44</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3357,12 @@
           <t>GUI-75</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Верхня навігаційна панель: логотип, назва, лінки, меню користувача</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Верхня навігаційна панель</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>TC-01, TC-10</t>
         </is>
@@ -3147,9 +3372,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Фіксована панель на всіх сторінках</t>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Назва, посилання, меню користувача</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3384,12 @@
           <t>GUI-80</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Форма створення теми форуму: обов'язкові поля, блокування порожніх</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Форма теми форуму й обов'язкові поля</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>TC-22, TC-23</t>
         </is>
@@ -3174,9 +3399,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Перевірка поля 'Тема' та напис 'Обов'язкове поле'</t>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Створення теми і блокування порожньої теми</t>
         </is>
       </c>
     </row>
@@ -3186,14 +3411,14 @@
           <t>GUI-90</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Кросбраузерність: коректне відображення в Chrome та Firefox</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>TC-01..TC-30</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Адаптивність 375–1920 px у Chrome і Firefox</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TC-29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3201,9 +3426,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Усі тести сумісні з Chrome і Firefox</t>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Два браузери, 1920 px і 375 px</t>
         </is>
       </c>
     </row>
@@ -3213,24 +3438,24 @@
           <t>BL-10</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>GradeCalculator.weightedTotal: розрахунок, сума ваг 100%, винятки</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>TC-28</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>weightedTotal: сума ваг 100%, винятки</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>BVA суми ваг 99.9% / 100% / 100.1%</t>
+          <t>Не покрито у Web UI</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Внутрішній розрахунок Java-модуля; JUnit 5 у Спринті 4</t>
         </is>
       </c>
     </row>
@@ -3240,24 +3465,24 @@
           <t>BL-20</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>GradeCalculator.ectsLetter: шкала A..F за строгими напіввідкритими інтервалами</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>TC-25, TC-26, TC-27</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ectsLetter: межі шкали A..F</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>TC-25, TC-26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>BVA стиків 59.99/60.00 та 94.99/95.00</t>
+          <t>Покрито через UI</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Стовпець ECTS відсутній (BUG-010); літера для 88.50 і межа 59.99/60.00 не перевірені</t>
         </is>
       </c>
     </row>
@@ -3267,24 +3492,24 @@
           <t>BL-30</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>GradeCalculator.latePenalty: штраф 10%/день, максимум 50%, 0 днів без штрафу</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>latePenalty: 10%/день, максимум 50%</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>TC-15, TC-16</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>1 день (-10%), 5 днів (-50%), 6 днів (-50% cap)</t>
+          <t>Покрито через UI</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Штраф не застосовується (BUG-007); межа 50% не перевірена (TC-16 blocked)</t>
         </is>
       </c>
     </row>
@@ -3294,24 +3519,24 @@
           <t>BL-40</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>QuizScorer: питання з 1 відповіддю (1.0 або 0.0), порожня відповідь = 0.0</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>questionScore: одна правильна відповідь</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>TC-18, TC-20</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Правильна відповідь та відсутність вибору</t>
+          <t>Покрито через UI</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Правильна відповідь і порожній вибір</t>
         </is>
       </c>
     </row>
@@ -3321,24 +3546,24 @@
           <t>BL-50</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>QuizScorer: питання з кількома відповідями, частковий бал, min 0.0, винятки</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>TC-20, TC-21</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>questionScore: кілька відповідей, частковий бал</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>TC-21</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Частковий бал (0.5 б.) та захист від від'ємного</t>
+          <t>Покрито через UI</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0.5 бала за 1 із 2 правильних; від'ємний бал не виникає</t>
         </is>
       </c>
     </row>
@@ -3348,24 +3573,24 @@
           <t>BL-60</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>QuizScorer.score: відсотковий підсумок тесту, заокруглення HALF_UP</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>score: відсоток спроби, HALF_UP</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>TC-18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Підсумковий розрахунок спроби</t>
+          <t>Покрито через UI</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Підсумок 100.00% за двома питаннями</t>
         </is>
       </c>
     </row>
@@ -3375,24 +3600,24 @@
           <t>BL-70</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>EnrollmentValidator.canEnroll: 4 передумови (ключ, період, місця, пререквізит)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>TC-08, TC-09, TC-29</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>canEnroll: ключ, період, місця, пререквізит</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>TC-08, TC-09</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Таблиця рішень DT-01, успіх і блокування</t>
+          <t>Покрито частково</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Через UI перевірено лише ключ; період/місця/пререквізит — JUnit 5</t>
         </is>
       </c>
     </row>
@@ -3402,24 +3627,24 @@
           <t>BL-80</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>EnrollmentValidator.violations: типізований список констант помилок</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>TC-09, TC-29</t>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>violations: точні рядки ERR_*</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Покрито повністю</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ERR_KEY, ERR_PREREQUISITE</t>
+          <t>Не покрито у Web UI</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Внутрішні константи Java-модуля; JUnit 5 у Спринті 4</t>
         </is>
       </c>
     </row>
@@ -3429,24 +3654,24 @@
           <t>P-10</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Час завантаження сторінки курсу &lt;= 3 с при 200 користувачах</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Сторінка курсу ≤ 3 с при 200 користувачах</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>TC-10</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Завантаження сторінки курсу за нормативом</t>
+          <t>Покрито частково</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Лише однокористувацький замір; навантаження на публічному demo заборонене</t>
         </is>
       </c>
     </row>
@@ -3456,24 +3681,24 @@
           <t>P-20</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Час завантаження статичних сторінок &lt;= 1.5 с</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>TC-01, TC-06</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Статичні сторінки ≤ 1.5 с при 200 користувачах</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Миттєвий відгук сторінок входу і каталогу</t>
+          <t>Не покрито</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Навантажувальний прогін 200 користувачів на публічному demo заборонений; окремого заміру в Спринті 3 не проводилося</t>
         </is>
       </c>
     </row>
@@ -3483,24 +3708,24 @@
           <t>S-10</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Зберігання паролів bcrypt, HTTPS TLS 1.3, автотаймаут 2 год</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>bcrypt, HTTPS, таймаут 2 год</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>TC-01</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>HTTPS з'єднання стенду, безпечна авторизація</t>
+          <t>Покрито частково</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>У TC-01 спостережено HTTPS; хеші паролів і таймаут недоступні на demo</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3735,12 @@
           <t>S-20</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Блокування на 15 хв після 3 невдалих спроб входу поспіль</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Блокування після 3 невдалих спроб</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>TC-03</t>
         </is>
@@ -3525,9 +3750,9 @@
           <t>Покрито повністю</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Перевірка блокування акаунту після 3 спроб</t>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Блокування відсутнє (BUG-002)</t>
         </is>
       </c>
     </row>
@@ -3537,24 +3762,24 @@
           <t>U-10</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Юзабіліті: виконання сценарію входу і відкриття курсу &lt;= 2 хв</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>TC-01, TC-08</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Сценарій входу й курсу ≤ 2 хв</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Швидка та інтуїтивна навігація</t>
+          <t>Не покрито</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Потрібна вибірка ≥ 10 користувачів; у Спринті 3 не проводилася</t>
         </is>
       </c>
     </row>
@@ -3564,24 +3789,24 @@
           <t>U-20</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Підтримка української та англійської мов інтерфейсу</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Українська та англійська локалізація</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>TC-01, TC-02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Повністю українська локалізація</t>
+          <t>Покрито частково</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Перевірено українські підписи форми входу; перемикання на англійську окремим кейсом не перевірялося</t>
         </is>
       </c>
     </row>
@@ -3591,24 +3816,24 @@
           <t>D-10</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Посібники користувача за стандартом IEEE 26514</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>TC-01..TC-30</t>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Посібники користувача за IEEE 26514</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Усі кроки співпадають з операціями F-10..F-130</t>
+          <t>Не покрито</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Документація постачається поза demo; перевірка не входить у Web UI-прогін</t>
         </is>
       </c>
     </row>
@@ -3618,24 +3843,24 @@
           <t>D-20</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Контекстна довідка (значок '?') біля полів форм входу та журналу</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>TC-01, TC-25</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Контекстна довідка «?» біля полів</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Покрито</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Наявність підказок біля ключових полів</t>
+          <t>Не покрито</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Контекстна довідка не перевірялася в UI-прогоні; винесено на Спринт 4</t>
         </is>
       </c>
     </row>
@@ -3653,53 +3878,53 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TC-ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Вимога SRS 1.1</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Заголовок тест-кейсу</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Рецензент</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Зауваження рецензента (§5.3 чек-лист)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Зауваження рецензента (§5.3)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Виправлено (так/ні)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -3711,29 +3936,29 @@
           <t>TC-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>F-10, GUI-10</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Успішний вхід студента за валідними логіном та паролем</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Успішний вхід студента з валідними обліковими даними та вихід із системи</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Уточнити фінальний крок виходу для забезпечення повної автономності (Zero Dependency).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Додано фінальний крок виходу для повної незалежності кейса.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3743,7 +3968,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3753,29 +3978,29 @@
           <t>TC-02</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>F-10, GUI-20</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Помилка входу при невірному паролі зі збереженням логіну</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Помилка входу з невірним паролем: збереження логіна, очищення пароля, фокус у полі «Пароль»</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Додати перевірку збереження значення в полі логіну та очищення пароля.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку фокуса клавіатурою, а не лише візуальним оглядом.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3785,7 +4010,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3795,29 +4020,29 @@
           <t>TC-03</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>F-10, S-20</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Блокування облікового запису на 15 хв після 3 невдалих спроб</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Блокування облікового запису на 15 хвилин після 3 невдалих спроб входу</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Деталізувати кроки для кожної з 3 послідовних спроб та зазначити текст про 15 хв.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Кожна спроба винесена в окремий крок; додано перевірку входу з правильним паролем після блокування.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3827,7 +4052,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3837,29 +4062,29 @@
           <t>TC-04</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>F-20</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Запит на скидання пароля за валідним зареєстрованим email</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Запит на відновлення пароля за зареєстрованим email</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Вказати, що посилання дійсне 30 хв згідно з F-20.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Уточнено, що перевірка завершується до відправлення листа (demo не надсилає пошту).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3869,7 +4094,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3879,29 +4104,29 @@
           <t>TC-05</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>F-20</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Запит на відновлення пароля з неіснуючим email</t>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Відновлення пароля для неіснуючого облікового запису без розкриття його відсутності</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Зафіксувати нейтральне повідомлення для захисту від перебору акаунтів.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Зафіксовано точний текст нейтрального повідомлення замість загального «без помилок».</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3911,7 +4136,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3921,29 +4146,29 @@
           <t>TC-06</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>F-30</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Пошук курсу в каталозі за валідним фрагментом назви</t>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Пошук курсу в каталозі за фрагментом назви без урахування регістру</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Уточнити умову нечутливості до регістру символів.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Вказано точний пошуковий рядок і очікувану назву курсу.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3953,7 +4178,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -3963,29 +4188,29 @@
           <t>TC-07</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>F-30</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Пошук курсу за неіснуючим фрагментом назви</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Пошук курсу за рядком, що не має збігів, із повідомленням про порожній результат</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Вказати конкретний рядок пошуку без збігів.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Вказано конкретний рядок без збігів і точний текст повідомлення.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3995,7 +4220,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4005,29 +4230,29 @@
           <t>TC-08</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>F-40</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Успішне самозарахування студента за точним кодовим словом</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>F-40, GUI-50, BL-70</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Самозарахування студента за точним кодовим словом із присвоєнням ролі «Студент»</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Додати перевірку присвоєння ролі 'Студент' після зарахування.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку ролі «Студент» у списку учасників.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4037,7 +4262,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4047,29 +4272,29 @@
           <t>TC-09</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>F-40, GUI-60</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Спроба самозарахування з невірним кодовим словом</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F-40, GUI-60, BL-70</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Відхилення самозарахування при кодовому слові з іншим регістром</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити точне місце виведення помилки (під полем) та очищення поля.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Уточнено місце виведення повідомлення (під полем) і очищення поля.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4079,7 +4304,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4089,29 +4314,29 @@
           <t>TC-10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>F-50</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Завантаження сторінки курсу та перевірка навігаційної панелі</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>F-50, GUI-75, P-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Сторінка курсу: секції, робочий лівий індекс і верхня навігаційна панель</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити наявність робочих гіперпосилань у лівій панелі навігації.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку робочих гіперпосилань лівого індексу.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4121,7 +4346,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4131,29 +4356,29 @@
           <t>TC-11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>F-60, GUI-30</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Здача практичного завдання до дедлайну з файлом .pdf</t>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Здача завдання файлом report.pdf до дедлайну зі зміною статусу</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Зафіксувати перехід у статус 'Здано для оцінювання' з датою і часом.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку дати й часу здачі, а не лише статусу.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,7 +4388,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4173,29 +4398,29 @@
           <t>TC-12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>F-60, GUI-30</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Спроба завантаження файлу недозволеного формату (.exe)</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GUI-30, F-60</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Блокування завантаження файлу .exe у формі здачі завдання</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Додати негативну перевірку блокування виконуваних файлів.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку, що статус не змінюється на «Здано» після відмови.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4205,7 +4430,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4215,29 +4440,29 @@
           <t>TC-13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>GUI-30</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка розміру файлу (20.00 МБ vs 20.01 МБ)</t>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Граничний розмір файлу: 20.00 МБ приймається, 20.01 МБ відхиляється</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Звузити крок BVA з 1 МБ до 0.01 МБ (20.00 МБ vs 20.01 МБ).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Межу звужено до 0.01 МБ: 20.00 МБ (b) і 20.01 МБ (b+1).</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4247,7 +4472,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4257,29 +4482,29 @@
           <t>TC-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>GUI-30</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка кількості файлів (5 шт. vs 6 шт.)</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Гранична кількість файлів: 5 приймаються, 6-й блокується</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Чітко виділити межу $b=5$ (приймається) та $b+1=6$ (блокується).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Явно позначено b=5 (приймається) і b+1=6 (блокується).</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4289,7 +4514,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4299,29 +4524,29 @@
           <t>TC-15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>F-60, BL-30</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Автоматичне нарахування штрафу 10% за 1 день запізнення</t>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Штраф 10% за здачу на один день пізніше дедлайну</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Синхронізувати ставку штрафу з BL-30 (10% замість застарілих 5%).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Ставку синхронізовано з BL-30 (10%), кроки створення даних додано.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4331,7 +4556,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4341,29 +4566,29 @@
           <t>TC-16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>F-60, BL-30</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка максимального порогу штрафу 50% (5 і 6 днів)</t>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Обмеження штрафу 50% при запізненні на 5 і 6 днів</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Позначити можливість блокування через баг автоштрафу на демо-стенді.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Додано два окремі дедлайни (5 і 6 днів) замість нествореного стану.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4373,7 +4598,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4383,29 +4608,29 @@
           <t>TC-17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>F-70</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Оцінювання практичної роботи викладачем з відгуком</t>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Оцінювання роботи викладачем із балом і текстовим відгуком</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити видимість виставленого балу в кабінеті студента.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку видимості бала й відгуку в кабінеті студента.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4415,7 +4640,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4425,29 +4650,29 @@
           <t>TC-18</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>F-80</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Успішне проходження тестування студентом</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>F-80, GUI-40, BL-60</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Проходження тесту з переходом між питаннями та автоматичним підрахунком</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Додати перевірку переходу між сторінками питань та збереження відповідей.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Додано перехід між сторінками питань і перевірку збереження відповідей.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4457,7 +4682,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4467,29 +4692,29 @@
           <t>TC-19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>F-80</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка ліміту спроб тестування (до 3 спроб)</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Ліміт 3 спроби тесту: четверта спроба недоступна</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Зафіксувати ліміт у 3 спроби згідно з виправленою вимогою DEF-01.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Кожна спроба — окремий крок; додано явну перевірку 4-ї спроби.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4499,7 +4724,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4509,29 +4734,29 @@
           <t>TC-20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>F-80, BL-40</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Завершення спроби тесту без вибору варіантів</t>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Завершення спроби тесту без жодної відповіді</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Вказати, що порожній вибір дає 0 балів без аварійного збою системи.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Зафіксовано 0.00 без винятку та без зависання.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4541,7 +4766,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4551,29 +4776,29 @@
           <t>TC-21</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>BL-50</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Нарахування часткового балу в тесті з множинним вибором</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>F-80, BL-50</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Частковий бал за питання з кількома правильними відповідями</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити математичну формулу без від'ємних результатів (min = 0).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Зафіксовано формулу часткового балу 0.5 і захист від від'ємного результату.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4583,7 +4808,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4593,29 +4818,29 @@
           <t>TC-22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>F-90, GUI-80</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Створення нової теми для обговорення на форумі курсу</t>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Створення викладачем нової теми форуму та доступність редагування автором</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Додати перевірку 30-хвилинного вікна редагування повідомлення автором.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку посилання «Редагувати» для автора замість непрактичної перевірки 30 хв.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4625,7 +4850,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4635,29 +4860,29 @@
           <t>TC-23</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>GUI-80</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Спроба створення теми форуму з порожнім полем 'Тема'</t>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Блокування публікації теми форуму з порожнім полем «Тема»</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Сфокусувати кейс суто на валідації обов'язкового поля теми.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Прибрано альтернативу «або браузерне сповіщення»; зафіксовано точний критерій.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4667,7 +4892,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4677,29 +4902,29 @@
           <t>TC-24</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>F-90</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Автоматичне маркування повідомлення зі стоп-словом</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Маркування повідомлення форуму зі стоп-словом для перевірки викладачем</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Вказати тестове слово зі стоп-словника та маркер 'Потребує перевірки'.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Замінено плейсхолдер [toxic_word] на конкретне слово «спойлер» зі словника.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4709,7 +4934,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4719,29 +4944,29 @@
           <t>TC-25</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>F-100, GUI-45</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Перегляд персонального журналу оцінок студентом</t>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Журнал оцінок студента: стовпці, підсумок і літера ECTS</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити наявність стовпця літери ECTS та жирне виділення підсумку.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Додано перевірку літери ECTS для конкретного підсумку 88.50.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4751,7 +4976,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4761,29 +4986,29 @@
           <t>TC-26</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>BL-20</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Гранична верифікація шкали ECTS на стику Fx та E (59.99 vs 60.00)</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>F-100, BL-20</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Межа шкали ECTS Fx/E у журналі оцінок: 59.99 і 60.00</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Вказати точні точки 59.99 б. (Fx) та 60.00 б. (E) за правилом DEF-04.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Замінено виклик Java-методу на UI-перевірку межі ECTS; кейс виконується на demo.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4793,7 +5018,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4803,29 +5028,29 @@
           <t>TC-27</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>BL-20</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Гранична верифікація шкали ECTS на стику B та A (94.99 vs 95.00)</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>F-110</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Редагування профілю студента та модерація зміни ПІБ</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Зафіксувати точки 94.99 б. (B) та 95.00 б. (A).</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Замінено Java-виклик на перевірку профілю та модерації ПІБ у Web UI.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4835,7 +5060,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4845,29 +5070,29 @@
           <t>TC-28</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>BL-10</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Гранична перевірка суми ваг оцінюваних елементів (99.9% vs 100%)</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>F-120</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Календар: події дедлайнів курсу та створення особистої події</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Вказати виняток IllegalArgumentException при сумі ваг != 100.0%.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Замінено Java-виклик на перевірку календаря; додано створення події.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4877,7 +5102,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4887,29 +5112,29 @@
           <t>TC-29</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BL-70, BL-80</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Перевірка блокування зарахування при невиконаному пререквізиті</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GUI-70, GUI-90</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Адаптивне подання календаря на 375 px і кросбраузерність Chrome/Firefox</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Зафіксувати строкову константу помилки ERR_PREREQUISITE.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Замінено Java-виклик на реальну адаптивну та кросбраузерну перевірку.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4919,7 +5144,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
@@ -4929,29 +5154,29 @@
           <t>TC-30</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>F-130</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Спроба створення курсу менеджером з дублюванням короткої назви</t>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Заборона створення курсу з дубльованою короткою назвою</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Панайотов О. (Scrum Master)</t>
+          <t>Панайотов О. (Скрам-майстер / Рецензент)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Перевірити блокування та виведення тексту про зайняту назву.</t>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>У передумовах явно створено курс QA-2026 (S3) замість припущення про наявний стан.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4961,7 +5186,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Approved ✓</t>
+          <t>Reviewed / Approved</t>
         </is>
       </c>
     </row>
